--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1253,6 +1253,240 @@
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120632248</v>
+      </c>
+      <c r="B7" t="n">
+        <v>102975</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>706</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svedjenäva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Geranium bohemicum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Stubbetorp 800m NO, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>603924</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6546188</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>hygge</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120632206</v>
+      </c>
+      <c r="B8" t="n">
+        <v>102975</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>706</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svedjenäva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Geranium bohemicum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Amsterdam 450m SO, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>603739</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6546307</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-23</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>hygge</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1487,6 +1487,116 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121505734</v>
+      </c>
+      <c r="B9" t="n">
+        <v>57788</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>102999</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Björktrast</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Turdus pilaris</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Amsterdam 500m so, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>603714</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6546199</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-06</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1492,7 +1492,7 @@
         <v>121505734</v>
       </c>
       <c r="B9" t="n">
-        <v>57788</v>
+        <v>57789</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1492,7 +1492,7 @@
         <v>121505734</v>
       </c>
       <c r="B9" t="n">
-        <v>57789</v>
+        <v>57790</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1597,6 +1597,113 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128111338</v>
+      </c>
+      <c r="B10" t="n">
+        <v>101728</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Amsterdam 500m so, Srm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>603714</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6546199</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Vägren skogsväg</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1602,7 +1602,7 @@
         <v>128111338</v>
       </c>
       <c r="B10" t="n">
-        <v>101728</v>
+        <v>101729</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1602,7 +1602,7 @@
         <v>128111338</v>
       </c>
       <c r="B10" t="n">
-        <v>101729</v>
+        <v>101730</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1602,7 +1602,7 @@
         <v>128111338</v>
       </c>
       <c r="B10" t="n">
-        <v>101730</v>
+        <v>101731</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1602,7 +1602,7 @@
         <v>128111338</v>
       </c>
       <c r="B10" t="n">
-        <v>101731</v>
+        <v>101739</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1602,7 +1602,7 @@
         <v>128111338</v>
       </c>
       <c r="B10" t="n">
-        <v>101739</v>
+        <v>101832</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1602,7 +1602,7 @@
         <v>128111338</v>
       </c>
       <c r="B10" t="n">
-        <v>101832</v>
+        <v>101848</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1602,7 +1602,7 @@
         <v>128111338</v>
       </c>
       <c r="B10" t="n">
-        <v>101848</v>
+        <v>101859</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>130305484</v>
       </c>
       <c r="B11" t="n">
-        <v>58263</v>
+        <v>58289</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>130305484</v>
       </c>
       <c r="B11" t="n">
-        <v>58289</v>
+        <v>58291</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>130305484</v>
       </c>
       <c r="B11" t="n">
-        <v>58291</v>
+        <v>58299</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>130305484</v>
       </c>
       <c r="B11" t="n">
-        <v>58299</v>
+        <v>58300</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -1709,7 +1709,7 @@
         <v>130305484</v>
       </c>
       <c r="B11" t="n">
-        <v>58300</v>
+        <v>58301</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>84956659</v>
+        <v>117301735</v>
       </c>
       <c r="B2" t="n">
-        <v>98932</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>224932</v>
+        <v>706</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig backsmörblomma</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Geranium bohemicum</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
@@ -711,14 +710,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Amsterdam 500m so, Srm</t>
+          <t>Amsterdam600 m SO, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603714.1514001715</v>
+        <v>603909</v>
       </c>
       <c r="R2" t="n">
-        <v>6546198.669155385</v>
+        <v>6546179</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -745,22 +744,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-04-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-05-26</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,7 +764,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Vägslänt</t>
+          <t>Åkerkant</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -793,15 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104679399</v>
+        <v>120632206</v>
       </c>
       <c r="B3" t="n">
-        <v>56522</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,38 +793,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205976</v>
+        <v>706</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gråkråka</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corvus corone cornix</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Amsterdam600 m SO, Srm</t>
+          <t>Amsterdam 450m SO, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>603908.6043258026</v>
+        <v>603739</v>
       </c>
       <c r="R3" t="n">
-        <v>6546178.711128755</v>
+        <v>6546307</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -867,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -891,8 +865,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>hygge</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,15 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104679375</v>
+        <v>120632248</v>
       </c>
       <c r="B4" t="n">
-        <v>56311</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104160</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,38 +905,38 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100067</v>
+        <v>706</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Havsörn</t>
+          <t>Svedjenäva</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Haliaeetus albicilla</t>
+          <t>Geranium bohemicum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Amsterdam600 m SO, Srm</t>
+          <t>Stubbetorp 800m NO, Srm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>603908.6043258026</v>
+        <v>603924</v>
       </c>
       <c r="R4" t="n">
-        <v>6546178.711128755</v>
+        <v>6546188</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -983,22 +963,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-11-13</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-10-23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,8 +977,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>hygge</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1025,15 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110578346</v>
+        <v>115932317</v>
       </c>
       <c r="B5" t="n">
-        <v>44331</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91333</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,39 +1017,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>201164</v>
+        <v>2008</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Amsterdam 500m so, Srm</t>
+          <t>Amsterdam 600m SO, Srm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>603714.1514001715</v>
+        <v>603890</v>
       </c>
       <c r="R5" t="n">
-        <v>6546198.669155385</v>
+        <v>6546239</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1100,22 +1074,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-07-04</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-04-13</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1127,6 +1091,11 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1143,43 +1112,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>117301735</v>
+        <v>104679375</v>
       </c>
       <c r="B6" t="n">
-        <v>102874</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>706</v>
+        <v>100067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1217,12 +1181,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-05-26</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,14 +1195,8 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Åkerkant</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1255,15 +1213,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120632248</v>
+        <v>121505734</v>
       </c>
       <c r="B7" t="n">
-        <v>103104</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1271,38 +1224,42 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>706</v>
+        <v>102999</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stubbetorp 800m NO, Srm</t>
+          <t>Amsterdam 500m so, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>603924</v>
+        <v>603714</v>
       </c>
       <c r="R7" t="n">
-        <v>6546188</v>
+        <v>6546199</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,12 +1286,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2024-12-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,19 +1300,8 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>hygge</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1372,15 +1318,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120632206</v>
+        <v>130305484</v>
       </c>
       <c r="B8" t="n">
-        <v>103104</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58393</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1388,27 +1329,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>706</v>
+        <v>102999</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svedjenäva</t>
+          <t>Björktrast</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Geranium bohemicum</t>
+          <t>Turdus pilaris</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1446,12 +1391,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-23</t>
+          <t>2025-12-26</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,19 +1405,8 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>hygge</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1489,58 +1423,49 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121505734</v>
+        <v>105540665</v>
       </c>
       <c r="B9" t="n">
-        <v>57791</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102999</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Amsterdam 500m so, Srm</t>
+          <t>Amsterdam600 m SO, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>603714</v>
+        <v>603909</v>
       </c>
       <c r="R9" t="n">
-        <v>6546199</v>
+        <v>6546179</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1567,12 +1492,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-12-06</t>
+          <t>2023-01-03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1599,38 +1524,39 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128111338</v>
+        <v>110578346</v>
       </c>
       <c r="B10" t="n">
-        <v>101859</v>
+        <v>45042</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221317</v>
+        <v>201164</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullklöver</t>
+          <t>Sexfläckig bastardsvärmare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Trifolium aureum</t>
+          <t>Zygaena filipendulae</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pollich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1668,12 +1594,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2025-08-31</t>
+          <t>2023-07-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1685,11 +1611,6 @@
       <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Vägren skogsväg</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1706,27 +1627,27 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130305484</v>
+        <v>104679399</v>
       </c>
       <c r="B11" t="n">
-        <v>58301</v>
+        <v>58085</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102999</v>
+        <v>205976</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Björktrast</t>
+          <t>Gråkråka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Turdus pilaris</t>
+          <t>Corvus corone cornix</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1734,25 +1655,21 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Amsterdam 450m SO, Srm</t>
+          <t>Amsterdam600 m SO, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>603739</v>
+        <v>603909</v>
       </c>
       <c r="R11" t="n">
-        <v>6546307</v>
+        <v>6546179</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1779,12 +1696,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2022-11-13</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,6 +1725,554 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>131846453</v>
+      </c>
+      <c r="B12" t="n">
+        <v>107943</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219933</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kattfot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Antennaria dioica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Gaertn.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Amsterdam 450m SO, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>603739</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6546307</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>99183253</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Stubbetorp 800m no, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>603991</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6546193</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2022-03-16</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2022-03-16</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Blandbarrskog</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>128111338</v>
+      </c>
+      <c r="B14" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Amsterdam 500m so, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>603714</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6546199</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-08-31</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Vägren skogsväg</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>84956484</v>
+      </c>
+      <c r="B15" t="n">
+        <v>102560</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222133</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Jungfrulin</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Polygala vulgaris</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Amsterdam 500m so, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>603714</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6546199</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>84956659</v>
+      </c>
+      <c r="B16" t="n">
+        <v>101746</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>224932</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vanlig backsmörblomma</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Amsterdam 500m so, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>603714</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6546199</v>
+      </c>
+      <c r="S16" t="n">
+        <v>25</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Flen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Helgesta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-04-29</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Vägslänt</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Rolf Olsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 37425-2023 artfynd.xlsx
+++ b/artfynd/A 37425-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117301735</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -891,6 +901,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632206</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1003,6 +1018,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120632248</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1109,6 +1129,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115932317</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1210,6 +1235,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104679375</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1315,6 +1345,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121505734</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1420,6 +1455,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/130305484</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1521,6 +1561,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105540665</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1624,6 +1669,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110578346</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1725,6 +1775,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104679399</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1832,6 +1887,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131846453</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1952,6 +2012,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99183253</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2059,6 +2124,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128111338</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2170,6 +2240,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84956484</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2273,8 +2348,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/84956659</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>